--- a/dist/output/abstract.xlsx
+++ b/dist/output/abstract.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UP24JDA222615</t>
+          <t>UP28SWF234567</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,32 +511,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0125</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UP24JDA250429</t>
+          <t>UP27SDF123456</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -599,42 +599,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UP24JDA250614</t>
+          <t>UP24SWF456789</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0141</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F4" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>42.5</v>
+        <v>58</v>
       </c>
       <c r="K4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="L4" t="n">
-        <v>87.5</v>
+        <v>76</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UP24JDA250617</t>
+          <t>UP20SDA890123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -658,34 +658,279 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F5" t="n">
+        <v>130</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>90</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UP21SDF789012</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>49</v>
+      </c>
+      <c r="F6" t="n">
+        <v>126</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>58</v>
+      </c>
+      <c r="K6" t="n">
         <v>38</v>
       </c>
-      <c r="F5" t="n">
-        <v>102</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>40</v>
-      </c>
-      <c r="L5" t="n">
-        <v>95</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L6" t="n">
+        <v>98</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UP22SDN678901</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>145</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" t="n">
+        <v>22</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UP23SWA345678</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" t="n">
+        <v>135</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>70</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UP25SWN567890</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>148</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>36</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" t="n">
+        <v>52</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UP26SWN901234</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>41</v>
+      </c>
+      <c r="F10" t="n">
+        <v>134</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>82</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
